--- a/fpga/V9968_Cartridge_TangNano20K/doc/tangnano20k_vdp_cartridge_ports.xlsx
+++ b/fpga/V9968_Cartridge_TangNano20K/doc/tangnano20k_vdp_cartridge_ports.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\TangCartMSX\RTL\tangnano20k_vdp_cartridge_rev2_step1\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\V9968_Cartridge\fpga\V9968_Cartridge_TangNano20K\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19CFAA3-E21A-4173-8332-0158F35B309E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13440" windowHeight="12945"/>
+    <workbookView xWindow="-10680" yWindow="1185" windowWidth="25065" windowHeight="15975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="86">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -371,11 +372,24 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>HDMI出力時使用不可</t>
+    <rPh sb="4" eb="6">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>シヨウフカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -597,7 +611,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -649,23 +663,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -946,7 +957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:N26"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -968,20 +979,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="2:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:14" x14ac:dyDescent="0.15">
@@ -1307,20 +1312,22 @@
       <c r="N12" s="3"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B13" s="2">
+      <c r="B13" s="10">
         <v>10</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="11">
         <v>5</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="3"/>
+      <c r="F13" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="12"/>
       <c r="I13" s="2">
         <v>31</v>
       </c>
@@ -1337,20 +1344,22 @@
       <c r="N13" s="3"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B14" s="2">
+      <c r="B14" s="10">
         <v>11</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="11">
         <v>5</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="3"/>
+      <c r="F14" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="12"/>
       <c r="I14" s="2">
         <v>30</v>
       </c>
@@ -1557,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="1"/>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="17" t="s">
         <v>79</v>
       </c>
       <c r="N20" s="3"/>
@@ -1575,7 +1584,7 @@
       <c r="E21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="17" t="s">
         <v>78</v>
       </c>
       <c r="G21" s="3"/>
@@ -1589,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="1"/>
-      <c r="M21" s="19" t="s">
+      <c r="M21" s="17" t="s">
         <v>80</v>
       </c>
       <c r="N21" s="3"/>
@@ -1623,7 +1632,7 @@
         <v>3</v>
       </c>
       <c r="L22" s="1"/>
-      <c r="M22" s="21" t="s">
+      <c r="M22" s="19" t="s">
         <v>82</v>
       </c>
       <c r="N22" s="3"/>
@@ -1657,13 +1666,13 @@
         <v>3</v>
       </c>
       <c r="L23" s="5"/>
-      <c r="M23" s="20" t="s">
+      <c r="M23" s="18" t="s">
         <v>83</v>
       </c>
       <c r="N23" s="6"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="20" t="s">
         <v>84</v>
       </c>
     </row>
